--- a/data/news/Codebook.xlsx
+++ b/data/news/Codebook.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olddominion-my.sharepoint.com/personal/jmart130_odu_edu/Documents/VMASC NLP/Academic Research Twitter Search (10M)/data/news/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olddominion-my.sharepoint.com/personal/jmart130_odu_edu/Documents/GITHUB_VMASC/twitter_analysis_col/data/news/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_F25DC773A252ABDACC1048DEA19E7B245ADE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3673E4C4-DE5D-426B-94DC-E745D4A015A8}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_F25DC773A252ABDACC1048DEA19E7B245ADE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C373612-4982-124B-89D1-AB75F8AF8AED}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="96">
   <si>
     <t>Category</t>
   </si>
@@ -1376,6 +1376,9 @@
   </si>
   <si>
     <t xml:space="preserve">Other Locals about Locals </t>
+  </si>
+  <si>
+    <t>Examples</t>
   </si>
 </sst>
 </file>
@@ -1531,7 +1534,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1647,92 +1650,104 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2014,15 +2029,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:D49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:E49"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="37.5" customWidth="1"/>
     <col min="3" max="3" width="43.33203125" customWidth="1"/>
-    <col min="4" max="4" width="82.77734375" customWidth="1"/>
+    <col min="4" max="4" width="82.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2032,439 +2047,442 @@
       <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
+      <c r="E2" s="28" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="B3" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B4" s="5"/>
-      <c r="C4" s="6" t="s">
+    <row r="4" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B4" s="23"/>
+      <c r="C4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B5" s="5"/>
-      <c r="C5" s="3" t="s">
+    <row r="5" spans="2:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="B5" s="23"/>
+      <c r="C5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B6" s="5"/>
-      <c r="C6" s="3" t="s">
+    <row r="6" spans="2:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="B6" s="23"/>
+      <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B7" s="5"/>
-      <c r="C7" s="3" t="s">
+    <row r="7" spans="2:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="B7" s="23"/>
+      <c r="C7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="5"/>
-      <c r="C8" s="3" t="s">
+    <row r="8" spans="2:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="B8" s="23"/>
+      <c r="C8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="5"/>
-      <c r="C9" s="3" t="s">
+    <row r="9" spans="2:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="B9" s="23"/>
+      <c r="C9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="5"/>
-      <c r="C10" s="6" t="s">
+    <row r="10" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B10" s="23"/>
+      <c r="C10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="5"/>
-      <c r="C11" s="6" t="s">
+    <row r="11" spans="2:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="B11" s="23"/>
+      <c r="C11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="5"/>
-      <c r="C12" s="10" t="s">
+    <row r="12" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="23"/>
+      <c r="C12" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B13" s="12" t="s">
+    <row r="13" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B13" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B14" s="5"/>
-      <c r="C14" s="3" t="s">
+    <row r="14" spans="2:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="B14" s="23"/>
+      <c r="C14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B15" s="5"/>
-      <c r="C15" s="3" t="s">
+    <row r="15" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B15" s="23"/>
+      <c r="C15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B16" s="5"/>
-      <c r="C16" s="3" t="s">
+    <row r="16" spans="2:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="B16" s="23"/>
+      <c r="C16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B17" s="5"/>
-      <c r="C17" s="3" t="s">
+    <row r="17" spans="2:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="B17" s="23"/>
+      <c r="C17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B18" s="5"/>
-      <c r="C18" s="3" t="s">
+    <row r="18" spans="2:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="B18" s="23"/>
+      <c r="C18" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B19" s="5"/>
-      <c r="C19" s="3" t="s">
+    <row r="19" spans="2:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="B19" s="23"/>
+      <c r="C19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="15"/>
-      <c r="C20" s="16" t="s">
+    <row r="20" spans="2:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="25"/>
+      <c r="C20" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="18" t="s">
+    <row r="21" spans="2:4" ht="49" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B22" s="20" t="s">
+    <row r="22" spans="2:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="B22" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="11" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B23" s="21"/>
-      <c r="C23" s="3" t="s">
+    <row r="23" spans="2:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="B23" s="27"/>
+      <c r="C23" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="2:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B24" s="21"/>
-      <c r="C24" s="3" t="s">
+    <row r="24" spans="2:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="B24" s="27"/>
+      <c r="C24" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B25" s="21"/>
-      <c r="C25" s="3" t="s">
+    <row r="25" spans="2:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="B25" s="27"/>
+      <c r="C25" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B26" s="21"/>
-      <c r="C26" s="3" t="s">
+    <row r="26" spans="2:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="B26" s="27"/>
+      <c r="C26" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B27" s="21"/>
-      <c r="C27" s="3" t="s">
+    <row r="27" spans="2:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="B27" s="27"/>
+      <c r="C27" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B28" s="21"/>
-      <c r="C28" s="3" t="s">
+    <row r="28" spans="2:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="B28" s="27"/>
+      <c r="C28" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="2:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="B29" s="21"/>
-      <c r="C29" s="3" t="s">
+    <row r="29" spans="2:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="B29" s="27"/>
+      <c r="C29" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B30" s="21"/>
-      <c r="C30" s="3" t="s">
+    <row r="30" spans="2:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="B30" s="27"/>
+      <c r="C30" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B31" s="21"/>
-      <c r="C31" s="3" t="s">
+    <row r="31" spans="2:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="B31" s="27"/>
+      <c r="C31" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B32" s="21"/>
-      <c r="C32" s="3" t="s">
+    <row r="32" spans="2:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="B32" s="27"/>
+      <c r="C32" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B33" s="21"/>
-      <c r="C33" s="3" t="s">
+    <row r="33" spans="2:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="B33" s="27"/>
+      <c r="C33" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="21"/>
-      <c r="C34" s="3" t="s">
+    <row r="34" spans="2:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="27"/>
+      <c r="C34" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B35" s="12" t="s">
+    <row r="35" spans="2:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="B35" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="22" t="s">
+      <c r="C35" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B36" s="5"/>
-      <c r="C36" s="6" t="s">
+    <row r="36" spans="2:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="B36" s="23"/>
+      <c r="C36" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="2:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B37" s="5"/>
-      <c r="C37" s="6" t="s">
+    <row r="37" spans="2:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="B37" s="23"/>
+      <c r="C37" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="6" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B38" s="5"/>
-      <c r="C38" s="6" t="s">
+    <row r="38" spans="2:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="B38" s="23"/>
+      <c r="C38" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B39" s="5"/>
-      <c r="C39" s="6" t="s">
+    <row r="39" spans="2:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="B39" s="23"/>
+      <c r="C39" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B40" s="5"/>
-      <c r="C40" s="23" t="s">
+    <row r="40" spans="2:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="B40" s="23"/>
+      <c r="C40" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="2:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B41" s="5"/>
-      <c r="C41" s="24" t="s">
+    <row r="41" spans="2:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="B41" s="23"/>
+      <c r="C41" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="25" t="s">
+      <c r="D41" s="19" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="42" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B42" s="5"/>
-      <c r="C42" s="6" t="s">
+    <row r="42" spans="2:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="B42" s="23"/>
+      <c r="C42" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="43" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B43" s="5"/>
-      <c r="C43" s="6" t="s">
+    <row r="43" spans="2:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="B43" s="23"/>
+      <c r="C43" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B44" s="5"/>
-      <c r="C44" s="23" t="s">
+    <row r="44" spans="2:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="B44" s="23"/>
+      <c r="C44" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="45" spans="2:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="5"/>
-      <c r="C45" s="26" t="s">
+    <row r="45" spans="2:4" ht="33" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="23"/>
+      <c r="C45" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D45" s="13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="2:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B46" s="12" t="s">
+    <row r="46" spans="2:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="B46" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="C46" s="27" t="s">
+      <c r="C46" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D46" s="9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="47" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B47" s="5"/>
-      <c r="C47" s="3" t="s">
+    <row r="47" spans="2:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="B47" s="23"/>
+      <c r="C47" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="3" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="48" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B48" s="5"/>
-      <c r="C48" s="3" t="s">
+    <row r="48" spans="2:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="B48" s="23"/>
+      <c r="C48" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="49" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="15"/>
-      <c r="C49" s="16" t="s">
+    <row r="49" spans="2:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="25"/>
+      <c r="C49" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="D49" s="17" t="s">
+      <c r="D49" s="13" t="s">
         <v>40</v>
       </c>
     </row>
